--- a/00__Docs/01__Design/4_QA/TC/TC_전체.xlsx
+++ b/00__Docs/01__Design/4_QA/TC/TC_전체.xlsx
@@ -867,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L546"/>
+  <dimension ref="A1:L560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31844,6 +31844,850 @@
       <c r="L546" s="36" t="inlineStr">
         <is>
           <t>2026-09-05: 기획서 :630(13장 '밤: 개봉·담기 프로그레스')과 :658(14장 #2-a '담기 속도')이 아직 담기를 시간이 드는 절차로 전제한다. BB-7/BB-14를 닫은 v2.7의 정리가 6.5.1·11장까지만 갔다. 구현이 옳고 문서 두 곳이 낡았다. 13장은 첫 검증 빌드의 범위 정의라 그대로 두면 만들지 않기로 한 기능이 빌드 조건에 남는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-021</t>
+        </is>
+      </c>
+      <c r="B547" s="36" t="inlineStr">
+        <is>
+          <t>5.4 / 3.2</t>
+        </is>
+      </c>
+      <c r="C547" s="36" t="inlineStr">
+        <is>
+          <t>5장</t>
+        </is>
+      </c>
+      <c r="D547" s="36" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="E547" s="36" t="inlineStr">
+        <is>
+          <t>권위</t>
+        </is>
+      </c>
+      <c r="F547" s="36" t="inlineStr">
+        <is>
+          <t>[2인 대결] 상대 팀 조리대를 조작할 수 없다 (얹기·집기 모두 거부)</t>
+        </is>
+      </c>
+      <c r="G547" s="36" t="inlineStr">
+        <is>
+          <t>1. 호스트=팀0, MPPM 가상 플레이어=팀1로 Battle_01 플레이
+2. 낮 페이즈에서 팀0 조리대에 빵 베이스를 올려 둔다
+3. 서버가 팀1 플레이어를 그 조리대 사거리 안(90.60, 1.10, 21.50)으로 옮긴다
+4. 팀1 손에 초콜릿을 쥐어 준다
+5. 클론 에디터에서 prep.UseRpc()를 두 번 보낸다(얹기 시도 + 집기 시도)</t>
+        </is>
+      </c>
+      <c r="H547" s="36" t="inlineStr">
+        <is>
+          <t>조리대 내용물과 팀1의 손이 모두 그대로다</t>
+        </is>
+      </c>
+      <c r="I547" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J547" s="36" t="inlineStr"/>
+      <c r="K547" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L547" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브 2인. 클론(clientId=1, team=1)이 pos=(90.60,1.08,21.50)에서 실제 RPC 송신. 전후 prep=[BreadBase] 불변, c1 hand=Chocolate 불변, phase=Day rem=97s. 사거리·페이즈가 원인이 아님은 TC-05C2-024 대조군으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-022</t>
+        </is>
+      </c>
+      <c r="B548" s="36" t="inlineStr">
+        <is>
+          <t>7.1 / 3.2</t>
+        </is>
+      </c>
+      <c r="C548" s="36" t="inlineStr">
+        <is>
+          <t>7장</t>
+        </is>
+      </c>
+      <c r="D548" s="36" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="E548" s="36" t="inlineStr">
+        <is>
+          <t>권위</t>
+        </is>
+      </c>
+      <c r="F548" s="36" t="inlineStr">
+        <is>
+          <t>[2인 대결] 상대 팀 선반에서 재료를 가져갈 수 없다</t>
+        </is>
+      </c>
+      <c r="G548" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-021과 같은 배치에서 클론이 팀0 IngredientShelf.TakeRpc(Almond)를 보낸다</t>
+        </is>
+      </c>
+      <c r="H548" s="36" t="inlineStr">
+        <is>
+          <t>팀0 재고 아몬드 수가 줄지 않고 팀1의 손도 그대로다</t>
+        </is>
+      </c>
+      <c r="I548" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J548" s="36" t="inlineStr"/>
+      <c r="K548" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L548" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브 2인. 전 almond=4 -&gt; 후 almond=4, c1 hand=Chocolate 불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-023</t>
+        </is>
+      </c>
+      <c r="B549" s="36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C549" s="36" t="inlineStr">
+        <is>
+          <t>8장</t>
+        </is>
+      </c>
+      <c r="D549" s="36" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="E549" s="36" t="inlineStr">
+        <is>
+          <t>권위</t>
+        </is>
+      </c>
+      <c r="F549" s="36" t="inlineStr">
+        <is>
+          <t>[2인 대결] 상대 팀 카페에 업그레이드를 설치할 수 없다</t>
+        </is>
+      </c>
+      <c r="G549" s="36" t="inlineStr">
+        <is>
+          <t>클론이 팀0 Cafe.InstallUpgradeRpc(ConveyorBelt)를 보낸다</t>
+        </is>
+      </c>
+      <c r="H549" s="36" t="inlineStr">
+        <is>
+          <t>팀0 UpgradeMask가 0에서 바뀌지 않는다</t>
+        </is>
+      </c>
+      <c r="I549" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J549" s="36" t="inlineStr"/>
+      <c r="K549" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L549" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브 2인. 전후 cafe0 UpgradeMask=0 불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-024</t>
+        </is>
+      </c>
+      <c r="B550" s="36" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="C550" s="36" t="inlineStr">
+        <is>
+          <t>5장</t>
+        </is>
+      </c>
+      <c r="D550" s="36" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="E550" s="36" t="inlineStr">
+        <is>
+          <t>권위</t>
+        </is>
+      </c>
+      <c r="F550" s="36" t="inlineStr">
+        <is>
+          <t>[대조군] 같은 위치·같은 페이즈에서 팀0 플레이어는 같은 조작이 성공한다</t>
+        </is>
+      </c>
+      <c r="G550" s="36" t="inlineStr">
+        <is>
+          <t>1. TC-05C2-021 직후, 호스트(팀0) 플레이어를 (90.60,1.10,21.50)으로 옮긴다
+2. 초콜릿을 들고 prep.UseRpc()
+3. 빈손으로 prep.UseRpc()</t>
+        </is>
+      </c>
+      <c r="H550" s="36" t="inlineStr">
+        <is>
+          <t>초콜릿이 얹혀 재료 2개 조립물이 되고, 두 번째 F로 조립물을 손에 든다</t>
+        </is>
+      </c>
+      <c r="I550" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J550" s="36" t="inlineStr"/>
+      <c r="K550" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L550" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브. prep=[BreadBase 조립 · 재료 2개] hand=empty -&gt; prep=[빈손] hand=ASSEMBLY(2). 팀1 거부가 사거리·페이즈 때문이 아님을 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-025</t>
+        </is>
+      </c>
+      <c r="B551" s="36" t="inlineStr">
+        <is>
+          <t>5.1 / 3.2</t>
+        </is>
+      </c>
+      <c r="C551" s="36" t="inlineStr">
+        <is>
+          <t>5장</t>
+        </is>
+      </c>
+      <c r="D551" s="36" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="E551" s="36" t="inlineStr">
+        <is>
+          <t>권위</t>
+        </is>
+      </c>
+      <c r="F551" s="36" t="inlineStr">
+        <is>
+          <t>[2인 대결] 상대 팀 오븐의 완성품을 가져갈 수 없다</t>
+        </is>
+      </c>
+      <c r="G551" s="36" t="inlineStr">
+        <is>
+          <t>1. 팀0이 오븐에서 브라우니를 완성시킨다
+2. 팀1 플레이어를 오븐 사거리(93.60,1.10,21.60)로 옮기고 손을 비운다
+3. 클론이 oven.UseRpc()를 두 번 보낸다</t>
+        </is>
+      </c>
+      <c r="H551" s="36" t="inlineStr">
+        <is>
+          <t>오븐에 완성품이 남고 팀1의 손은 빈 상태다</t>
+        </is>
+      </c>
+      <c r="I551" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J551" s="36" t="inlineStr"/>
+      <c r="K551" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L551" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브 2인. oven=[ChocoBrownie (탄 것)] 유지, c1 hand=empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-026</t>
+        </is>
+      </c>
+      <c r="B552" s="36" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="C552" s="36" t="inlineStr">
+        <is>
+          <t>3장</t>
+        </is>
+      </c>
+      <c r="D552" s="36" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="E552" s="36" t="inlineStr">
+        <is>
+          <t>복제</t>
+        </is>
+      </c>
+      <c r="F552" s="36" t="inlineStr">
+        <is>
+          <t>[2인 대결] 상대 팀 카페 NetworkObject 자체가 클라이언트에 복제되지 않는다</t>
+        </is>
+      </c>
+      <c r="G552" s="36" t="inlineStr">
+        <is>
+          <t>클론 에디터에서 MatchDirector.Instance.CafeOf(t) (t=0..3)와 씬의 Cafe 컴포넌트를 모두 센다</t>
+        </is>
+      </c>
+      <c r="H552" s="36" t="inlineStr">
+        <is>
+          <t>자기 팀(1) 카페 하나만 보이고 나머지는 null이다</t>
+        </is>
+      </c>
+      <c r="I552" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J552" s="36" t="inlineStr"/>
+      <c r="K552" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L552" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브. 클론에서 cafe0/2/3=null, cafe1=Cafe(Clone)@(136,0,-20), 씬 Cafe count=1. 위 TC-05C2-021~025는 이 가시성을 서버에서 NetworkShow(1)로 강제 해제해 RPC를 실제로 보낼 수 있게 만든 뒤 수행했다</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="36" t="inlineStr">
+        <is>
+          <t>TC-BND-021</t>
+        </is>
+      </c>
+      <c r="B553" s="36" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="C553" s="36" t="inlineStr">
+        <is>
+          <t>6장</t>
+        </is>
+      </c>
+      <c r="D553" s="36" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="E553" s="36" t="inlineStr">
+        <is>
+          <t>밤</t>
+        </is>
+      </c>
+      <c r="F553" s="36" t="inlineStr">
+        <is>
+          <t>[경계·허용] 대시 쿨다운 실측값이 5~8초 안이다 (기획서 6.6)</t>
+        </is>
+      </c>
+      <c r="G553" s="36" t="inlineStr">
+        <is>
+          <t>1. Battle_01을 2인(호스트+MPPM)으로 플레이
+2. 씬의 DashHarass 인스턴스를 모두 찾아 Cooldown을 읽는다</t>
+        </is>
+      </c>
+      <c r="H553" s="36" t="inlineStr">
+        <is>
+          <t>모든 인스턴스의 cooldown이 5 이상 8 이하</t>
+        </is>
+      </c>
+      <c r="I553" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J553" s="36" t="inlineStr">
+        <is>
+          <t>BB-18</t>
+        </is>
+      </c>
+      <c r="K553" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L553" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브. Player(Clone) 2개 모두 cooldown=6, inRange=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="36" t="inlineStr">
+        <is>
+          <t>TC-BND-022</t>
+        </is>
+      </c>
+      <c r="B554" s="36" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="C554" s="36" t="inlineStr">
+        <is>
+          <t>6장</t>
+        </is>
+      </c>
+      <c r="D554" s="36" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="E554" s="36" t="inlineStr">
+        <is>
+          <t>밤</t>
+        </is>
+      </c>
+      <c r="F554" s="36" t="inlineStr">
+        <is>
+          <t>[경계·거부] 대시 쿨다운 필드에 [Range(5,8)]이 붙어 인스펙터에서 범위를 벗어난 값을 넣을 수 없다</t>
+        </is>
+      </c>
+      <c r="G554" s="36" t="inlineStr">
+        <is>
+          <t>DashHarass.cooldown 필드의 RangeAttribute를 리플렉션으로 읽는다</t>
+        </is>
+      </c>
+      <c r="H554" s="36" t="inlineStr">
+        <is>
+          <t>RangeAttribute min=5, max=8</t>
+        </is>
+      </c>
+      <c r="I554" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J554" s="36" t="inlineStr">
+        <is>
+          <t>BB-18</t>
+        </is>
+      </c>
+      <c r="K554" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L554" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브 리플렉션 확인: RangeAttribute min=5 max=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-027</t>
+        </is>
+      </c>
+      <c r="B555" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C555" s="36" t="inlineStr">
+        <is>
+          <t>4장</t>
+        </is>
+      </c>
+      <c r="D555" s="36" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="E555" s="36" t="inlineStr">
+        <is>
+          <t>페이즈</t>
+        </is>
+      </c>
+      <c r="F555" s="36" t="inlineStr">
+        <is>
+          <t>7일차가 끝나면 매치가 종료되고 8일차로 넘어가지 않는다</t>
+        </is>
+      </c>
+      <c r="G555" s="36" t="inlineStr">
+        <is>
+          <t>1. 플레이 중 SkipToNextDayServer()로 1일 -&gt; 7일까지 진행
+2. 7일차 밤/낮/전환을 EndPhaseNowServer()로 마감
+3. 이후에도 EndPhaseNowServer()를 3회 더 호출한다</t>
+        </is>
+      </c>
+      <c r="H555" s="36" t="inlineStr">
+        <is>
+          <t>7일차 전환이 끝나면 Finished=true, Day는 7에서 멈추고 새 밤이 시작되지 않는다</t>
+        </is>
+      </c>
+      <c r="I555" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J555" s="36" t="inlineStr">
+        <is>
+          <t>BB-13</t>
+        </is>
+      </c>
+      <c r="K555" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L555" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브 관찰: day=7 Transition -&gt; finished=True. 이후 EndPhaseNow 4회에도 day=7 phase=Transition finished=True 고정(GamePhase.EndPhaseNowServer의 finished 가드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-028</t>
+        </is>
+      </c>
+      <c r="B556" s="36" t="inlineStr">
+        <is>
+          <t>4 / 5.1</t>
+        </is>
+      </c>
+      <c r="C556" s="36" t="inlineStr">
+        <is>
+          <t>5장</t>
+        </is>
+      </c>
+      <c r="D556" s="36" t="inlineStr">
+        <is>
+          <t>회귀고정</t>
+        </is>
+      </c>
+      <c r="E556" s="36" t="inlineStr">
+        <is>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="F556" s="36" t="inlineStr">
+        <is>
+          <t>낮이 끝나면 조리가 멈추고 밤에는 완성 게이지가 붙지 않는다</t>
+        </is>
+      </c>
+      <c r="G556" s="36" t="inlineStr">
+        <is>
+          <t>1. 낮 끝 무렵 오븐에 조립물을 넣고 조리를 시작한다
+2. 낮 -&gt; 전환 -&gt; 밤으로 넘긴다
+3. 밤에서 오븐 상태를 읽는다
+4. 다음 낮으로 넘겨 다시 읽는다</t>
+        </is>
+      </c>
+      <c r="H556" s="36" t="inlineStr">
+        <is>
+          <t>밤에는 CookRemaining=0이어도 게이지가 붙지 않고, 다음 낮에 게이지가 붙어 완성된다</t>
+        </is>
+      </c>
+      <c r="I556" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J556" s="36" t="inlineStr"/>
+      <c r="K556" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L556" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 라이브. 밤(day2)에서 oven=[BreadBase][Cream] rem=0 gauge=False, 낮으로 넘긴 뒤 gauge=True -&gt; oven=[CreamCake]. Station.ShouldBeginGauge의 Phase.Day 조건과 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-029</t>
+        </is>
+      </c>
+      <c r="B557" s="36" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C557" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D557" s="36" t="inlineStr">
+        <is>
+          <t>회귀고정</t>
+        </is>
+      </c>
+      <c r="E557" s="36" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="F557" s="36" t="inlineStr">
+        <is>
+          <t>EditMode 테스트 전원 통과</t>
+        </is>
+      </c>
+      <c r="G557" s="36" t="inlineStr">
+        <is>
+          <t>unity command run_tests (mode=editor)</t>
+        </is>
+      </c>
+      <c r="H557" s="36" t="inlineStr">
+        <is>
+          <t>101/101 통과</t>
+        </is>
+      </c>
+      <c r="I557" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J557" s="36" t="inlineStr"/>
+      <c r="K557" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L557" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05 실행: 'EditMode complete: 101/101 passed', duration 4.8s. PlayMode 테스트는 0건(존재하지 않음, status=completed total=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="36" t="inlineStr">
+        <is>
+          <t>TC-05C2-030</t>
+        </is>
+      </c>
+      <c r="B558" s="36" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C558" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D558" s="36" t="inlineStr">
+        <is>
+          <t>회귀고정</t>
+        </is>
+      </c>
+      <c r="E558" s="36" t="inlineStr">
+        <is>
+          <t>런타임</t>
+        </is>
+      </c>
+      <c r="F558" s="36" t="inlineStr">
+        <is>
+          <t>2인 라이브 플레이 중 Console에 게임 오류·경고가 없다</t>
+        </is>
+      </c>
+      <c r="G558" s="36" t="inlineStr">
+        <is>
+          <t>1. clear_console 후 플레이
+2. 세션 종료 시 get_console_logs로 전체를 읽는다</t>
+        </is>
+      </c>
+      <c r="H558" s="36" t="inlineStr">
+        <is>
+          <t>게임 코드가 낸 Error/Warning 0건, Missing Script/Reference 0건, 스폰 실패 0건</t>
+        </is>
+      </c>
+      <c r="I558" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J558" s="36" t="inlineStr"/>
+      <c r="K558" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L558" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05. get_console_logs total=1이며 그 1건은 게임이 아니라 Pipeline CLI의 'Failed to handle /api/exec request: Main thread operation timed out after 5000ms'. Editor.log에 남은 [Netcode] NetworkPrefab ... missing a NetworkObject / nested NetworkObjects 경고는 오늘 이전 세션 것이며, 현재 DefaultNetworkPrefabs.asset 6개 엔트리를 실측한 결과 루트 NetworkObject 누락·중첩 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="36" t="inlineStr">
+        <is>
+          <t>TC-BND-023</t>
+        </is>
+      </c>
+      <c r="B559" s="36" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="C559" s="36" t="inlineStr">
+        <is>
+          <t>3장</t>
+        </is>
+      </c>
+      <c r="D559" s="36" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="E559" s="36" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="F559" s="36" t="inlineStr">
+        <is>
+          <t>[2인 전제] 호스트와 MPPM 가상 플레이어의 NetworkConfig가 동일하다 (낡은 클론이 아님)</t>
+        </is>
+      </c>
+      <c r="G559" s="36" t="inlineStr">
+        <is>
+          <t>두 에디터에서 Resources/NetworkManager 프리팹의 NetworkConfig.GetConfig(false)를 각각 읽어 대조한다</t>
+        </is>
+      </c>
+      <c r="H559" s="36" t="inlineStr">
+        <is>
+          <t>해시가 같고 transport/tick/scene management가 같다</t>
+        </is>
+      </c>
+      <c r="I559" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J559" s="36" t="inlineStr"/>
+      <c r="K559" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L559" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05. 양쪽 모두 hash=4486297275751797064 prefabs=0 tick=60 sceneMgmt=True transport=UnityTransport. 이후 실제 접속에서 clients=2, client0=team0(호스트) / client1=team1(클론) 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="36" t="inlineStr">
+        <is>
+          <t>TC-BND-024</t>
+        </is>
+      </c>
+      <c r="B560" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C560" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D560" s="36" t="inlineStr">
+        <is>
+          <t>회귀고정</t>
+        </is>
+      </c>
+      <c r="E560" s="36" t="inlineStr">
+        <is>
+          <t>런타임</t>
+        </is>
+      </c>
+      <c r="F560" s="36" t="inlineStr">
+        <is>
+          <t>2인 세션이 예고 없이 종료되지 않는다</t>
+        </is>
+      </c>
+      <c r="G560" s="36" t="inlineStr">
+        <is>
+          <t>1. Battle_01을 2인(호스트+MPPM)으로 플레이
+2. 호스트와 클론 양쪽에서 unity command eval을 번갈아 여러 번 실행하며 20~30분 진행</t>
+        </is>
+      </c>
+      <c r="H560" s="36" t="inlineStr">
+        <is>
+          <t>플레이 모드가 유지된다</t>
+        </is>
+      </c>
+      <c r="I560" s="36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J560" s="36" t="inlineStr">
+        <is>
+          <t>BB-36</t>
+        </is>
+      </c>
+      <c r="K560" s="36" t="inlineStr">
+        <is>
+          <t>런타임 회귀</t>
+        </is>
+      </c>
+      <c r="L560" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-05. 두 차례(각각 클론 쪽 eval을 주고받은 직후) 콘솔에 게임 오류 없이 호스트 플레이 모드가 stopped로 떨어졌다. 클론 Editor.log에는 Title 씬 로드가 남았다(SteamLobby.OnNetworkStopped 경로). 원인은 미확정 — QA 도구(eval의 메인 스레드 점유)일 수도, NetworkManager 종료 시 무조건 타이틀로 돌아가는 처리일 수도 있다. 재현 후 계속 진행은 가능했다</t>
         </is>
       </c>
     </row>
